--- a/03_Outputs/all/01_TablasDescriptivas/idx8_demografica.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx8_demografica.xlsx
@@ -399,7 +399,7 @@
         <v>-18.36531089959454</v>
       </c>
       <c r="D2">
-        <v>7.151854595179103</v>
+        <v>7.151854595179104</v>
       </c>
       <c r="E2">
         <v>-43.296124548071</v>
@@ -421,7 +421,7 @@
         <v>-65.96071046914989</v>
       </c>
       <c r="D3">
-        <v>9.394278152194435</v>
+        <v>9.394278152194431</v>
       </c>
       <c r="E3">
         <v>-100.724637681159</v>
@@ -465,7 +465,7 @@
         <v>-66.27078933671211</v>
       </c>
       <c r="D5">
-        <v>8.505819760561371</v>
+        <v>8.505819760561369</v>
       </c>
       <c r="E5">
         <v>-96.89863842662631</v>
@@ -487,7 +487,7 @@
         <v>-62.60798411280962</v>
       </c>
       <c r="D6">
-        <v>7.997597754705824</v>
+        <v>7.997597754705825</v>
       </c>
       <c r="E6">
         <v>-87.53246753246751</v>
@@ -509,7 +509,7 @@
         <v>-61.96893945311125</v>
       </c>
       <c r="D7">
-        <v>9.278084392400382</v>
+        <v>9.27808439240038</v>
       </c>
       <c r="E7">
         <v>-97.48520710059169</v>
@@ -531,7 +531,7 @@
         <v>-63.38192921835226</v>
       </c>
       <c r="D8">
-        <v>8.745296741418892</v>
+        <v>8.74529674141889</v>
       </c>
       <c r="E8">
         <v>-105.504587155963</v>

--- a/03_Outputs/all/01_TablasDescriptivas/idx8_demografica.xlsx
+++ b/03_Outputs/all/01_TablasDescriptivas/idx8_demografica.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -562,6 +562,72 @@
         <v>87.1202916160389</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Índice dep. econ. (rural)</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>125</v>
+      </c>
+      <c r="C10">
+        <v>-69.83383975011427</v>
+      </c>
+      <c r="D10">
+        <v>11.80548507438457</v>
+      </c>
+      <c r="E10">
+        <v>-133.601756954612</v>
+      </c>
+      <c r="F10">
+        <v>-45.5640097510527</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Índice dep. econ. H (rural)</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>125</v>
+      </c>
+      <c r="C11">
+        <v>-69.89779943328362</v>
+      </c>
+      <c r="D11">
+        <v>12.95613613196417</v>
+      </c>
+      <c r="E11">
+        <v>-135.507246376812</v>
+      </c>
+      <c r="F11">
+        <v>-35.9003632589517</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Índice dep. econ. M (rural)</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>125</v>
+      </c>
+      <c r="C12">
+        <v>-70.02824710744584</v>
+      </c>
+      <c r="D12">
+        <v>11.19067706180155</v>
+      </c>
+      <c r="E12">
+        <v>-131.656804733728</v>
+      </c>
+      <c r="F12">
+        <v>-45.4612819562801</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
